--- a/data/source/driver_default.xlsx
+++ b/data/source/driver_default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76929c7f1b9de68b/Documents/Dada/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="11_EDD44E5993BC482A58B3BF0BF84E774AB1880010" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B80AF70E-A6B3-4B67-845B-D9D5B0AA5438}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="11_EDD44E5993BC482A58B3BF0BF84E774AB1880010" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9227132A-29C9-45D5-B474-02753C885BE6}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="16200" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -167,9 +167,6 @@
     <t>LIN</t>
   </si>
   <si>
-    <t>Valterri Bottas</t>
-  </si>
-  <si>
     <t>BOT</t>
   </si>
   <si>
@@ -225,6 +222,9 @@
   </si>
   <si>
     <t>mexico.png</t>
+  </si>
+  <si>
+    <t>Valtteri Bottas</t>
   </si>
 </sst>
 </file>
@@ -280,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -293,9 +293,6 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,8 +626,8 @@
       <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>48</v>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -647,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -664,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -681,7 +678,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -698,7 +695,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -715,7 +712,7 @@
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -732,7 +729,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -749,7 +746,7 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -766,7 +763,7 @@
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -783,7 +780,7 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -800,7 +797,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -817,7 +814,7 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -834,7 +831,7 @@
         <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -851,7 +848,7 @@
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -868,7 +865,7 @@
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -885,7 +882,7 @@
         <v>8</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -902,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -919,7 +916,7 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -936,7 +933,7 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -953,7 +950,7 @@
         <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -970,15 +967,15 @@
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
         <v>44</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
       </c>
       <c r="C22" s="4">
         <v>86</v>
@@ -987,15 +984,15 @@
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
         <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>47</v>
       </c>
       <c r="C23" s="4">
         <v>86</v>
@@ -1004,7 +1001,7 @@
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
